--- a/manpower_log/Factory.xlsx
+++ b/manpower_log/Factory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\manpower_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC2BE4E-DE71-4E42-8DF8-89F9230E4548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B18E7A-DDBF-441F-9C9D-43D77C36DFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FB5B164-7150-4FBC-9B5E-59DE9D4F0071}"/>
   </bookViews>
